--- a/articles_raw.xlsx
+++ b/articles_raw.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N125"/>
+  <dimension ref="A1:N145"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -4255,12 +4255,12 @@
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>Target-Aware Fusion for RGB-T Pedestrian Detection</t>
+          <t>RTFNet: RGB-Thermal Fusion Network for Semantic Segmentation of Urban Scenes</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>target-aware fusion for rgb-t pedestrian detection</t>
+          <t>rtfnet: rgb-thermal fusion network for semantic segmentation of urban scenes</t>
         </is>
       </c>
       <c r="G96" t="inlineStr"/>
@@ -4291,12 +4291,12 @@
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>RTFNet: RGB-Thermal Fusion Network for Semantic Segmentation</t>
+          <t>EGFNet: Edge-Aware Guidance Fusion Network for RGB–Thermal Urban Scene Parsing</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>rtfnet: rgb-thermal fusion network for semantic segmentation</t>
+          <t>egfnet: edge-aware guidance fusion network for rgb–thermal urban scene parsing</t>
         </is>
       </c>
       <c r="G97" t="inlineStr"/>
@@ -4327,12 +4327,12 @@
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>Efficient RGB-T Tracking via Cross-Modality Distillation</t>
+          <t>Robust RGB-T Object Detection via Quality-Aware Decision Fusion</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>efficient rgb-t tracking via cross-modality distillation</t>
+          <t>robust rgb-t object detection via quality-aware decision fusion</t>
         </is>
       </c>
       <c r="G98" t="inlineStr"/>
@@ -4363,12 +4363,12 @@
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>Enhanced Thermal-RGB Fusion for Robust Object Detection</t>
+          <t>Siamese Network with Hybrid Fusion Strategy for RGB-T Tracking</t>
         </is>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>enhanced thermal-rgb fusion for robust object detection</t>
+          <t>siamese network with hybrid fusion strategy for rgb-t tracking</t>
         </is>
       </c>
       <c r="G99" t="inlineStr"/>
@@ -4399,12 +4399,12 @@
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>Siamese Network with Hybrid Fusion Strategy for RGB-T Tracking</t>
+          <t>Efficient RGB-T Tracking via Cross-Modality Distillation</t>
         </is>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>siamese network with hybrid fusion strategy for rgb-t tracking</t>
+          <t>efficient rgb-t tracking via cross-modality distillation</t>
         </is>
       </c>
       <c r="G100" t="inlineStr"/>
@@ -4435,12 +4435,12 @@
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>Robust RGB-T Object Detection via Decision Fusion</t>
+          <t>Enhanced Thermal-RGB Fusion for Robust Object Detection</t>
         </is>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>robust rgb-t object detection via decision fusion</t>
+          <t>enhanced thermal-rgb fusion for robust object detection</t>
         </is>
       </c>
       <c r="G101" t="inlineStr"/>
@@ -4471,12 +4471,12 @@
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>EGFNet: Edge-Aware RGB-T Fusion Network</t>
+          <t>Adaptive Hierarchical Feature Difference Auto-Encoder for RGB-T Tracking</t>
         </is>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>egfnet: edge-aware rgb-t fusion network</t>
+          <t>adaptive hierarchical feature difference auto-encoder for rgb-t tracking</t>
         </is>
       </c>
       <c r="G102" t="inlineStr"/>
@@ -4507,12 +4507,12 @@
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>DBCNet: Cross-Fusion Network for Urban Scene Understanding</t>
+          <t>Multi-Modal Fusion for End-to-End RGB-T Tracking</t>
         </is>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>dbcnet: cross-fusion network for urban scene understanding</t>
+          <t>multi-modal fusion for end-to-end rgb-t tracking</t>
         </is>
       </c>
       <c r="G103" t="inlineStr"/>
@@ -4543,12 +4543,12 @@
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>ABMDRNet: RGB-T Semantic Segmentation Network</t>
+          <t>Dynamic Bilateral Cross-Fusion Network for RGB-T Urban Scene Understanding</t>
         </is>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>abmdrnet: rgb-t semantic segmentation network</t>
+          <t>dynamic bilateral cross-fusion network for rgb-t urban scene understanding</t>
         </is>
       </c>
       <c r="G104" t="inlineStr"/>
@@ -4579,12 +4579,12 @@
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>Autonomous Driving with Thermal Fusion</t>
+          <t>Embedded Control Gate Fusion for RGB-T Scene Parsing</t>
         </is>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>autonomous driving with thermal fusion</t>
+          <t>embedded control gate fusion for rgb-t scene parsing</t>
         </is>
       </c>
       <c r="G105" t="inlineStr"/>
@@ -4615,12 +4615,12 @@
       </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t>Multi-Modal Fusion for RGB-T Tracking</t>
+          <t>Multiscale Feature Fusion Network for RGB-T Urban Road Scene Parsing</t>
         </is>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>multi-modal fusion for rgb-t tracking</t>
+          <t>multiscale feature fusion network for rgb-t urban road scene parsing</t>
         </is>
       </c>
       <c r="G106" t="inlineStr"/>
@@ -4651,12 +4651,12 @@
       </c>
       <c r="E107" t="inlineStr">
         <is>
-          <t>Visible-Infrared Fusion for Object Detection</t>
+          <t>Cross-Modality Fusion Transformer for RGB-T Object Detection</t>
         </is>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>visible-infrared fusion for object detection</t>
+          <t>cross-modality fusion transformer for rgb-t object detection</t>
         </is>
       </c>
       <c r="G107" t="inlineStr"/>
@@ -4687,12 +4687,12 @@
       </c>
       <c r="E108" t="inlineStr">
         <is>
-          <t>Cross-Modal Learning for RGB-T Detection</t>
+          <t>RGB-Thermal Fusion for Pedestrian Detection in Adverse Weather</t>
         </is>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>cross-modal learning for rgb-t detection</t>
+          <t>rgb-thermal fusion for pedestrian detection in adverse weather</t>
         </is>
       </c>
       <c r="G108" t="inlineStr"/>
@@ -4723,12 +4723,12 @@
       </c>
       <c r="E109" t="inlineStr">
         <is>
-          <t>Deep Multimodal Fusion for Pedestrian Detection</t>
+          <t>Deep Multimodal Fusion for Nighttime Object Detection</t>
         </is>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>deep multimodal fusion for pedestrian detection</t>
+          <t>deep multimodal fusion for nighttime object detection</t>
         </is>
       </c>
       <c r="G109" t="inlineStr"/>
@@ -4759,12 +4759,12 @@
       </c>
       <c r="E110" t="inlineStr">
         <is>
-          <t>Thermal-RGB Fusion for Night Vision Systems</t>
+          <t>Infrared-Visible Fusion for Robust Tracking in Foggy Conditions</t>
         </is>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>thermal-rgb fusion for night vision systems</t>
+          <t>infrared-visible fusion for robust tracking in foggy conditions</t>
         </is>
       </c>
       <c r="G110" t="inlineStr"/>
@@ -4795,12 +4795,12 @@
       </c>
       <c r="E111" t="inlineStr">
         <is>
-          <t>Attention-Based RGB-T Fusion Network</t>
+          <t>Attention-Based RGB-T Fusion for Low-Light Detection</t>
         </is>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>attention-based rgb-t fusion network</t>
+          <t>attention-based rgb-t fusion for low-light detection</t>
         </is>
       </c>
       <c r="G111" t="inlineStr"/>
@@ -4831,12 +4831,12 @@
       </c>
       <c r="E112" t="inlineStr">
         <is>
-          <t>Multispectral Fusion for Autonomous Driving</t>
+          <t>Dual-Stream Network for RGB-T Semantic Segmentation</t>
         </is>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>multispectral fusion for autonomous driving</t>
+          <t>dual-stream network for rgb-t semantic segmentation</t>
         </is>
       </c>
       <c r="G112" t="inlineStr"/>
@@ -4867,12 +4867,12 @@
       </c>
       <c r="E113" t="inlineStr">
         <is>
-          <t>Deep Fusion for Adverse Weather Detection</t>
+          <t>Transformer-Based RGB-T Fusion for Object Tracking</t>
         </is>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>deep fusion for adverse weather detection</t>
+          <t>transformer-based rgb-t fusion for object tracking</t>
         </is>
       </c>
       <c r="G113" t="inlineStr"/>
@@ -4903,12 +4903,12 @@
       </c>
       <c r="E114" t="inlineStr">
         <is>
-          <t>RGB-T Semantic Segmentation with Transformers</t>
+          <t>RGB-T Fusion with Domain Adaptation for Night Scenes</t>
         </is>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>rgb-t semantic segmentation with transformers</t>
+          <t>rgb-t fusion with domain adaptation for night scenes</t>
         </is>
       </c>
       <c r="G114" t="inlineStr"/>
@@ -4939,12 +4939,12 @@
       </c>
       <c r="E115" t="inlineStr">
         <is>
-          <t>Robust Tracking with Multimodal Fusion</t>
+          <t>Multimodal Feature Fusion for Robust Autonomous Driving Perception</t>
         </is>
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>robust tracking with multimodal fusion</t>
+          <t>multimodal feature fusion for robust autonomous driving perception</t>
         </is>
       </c>
       <c r="G115" t="inlineStr"/>
@@ -4975,12 +4975,12 @@
       </c>
       <c r="E116" t="inlineStr">
         <is>
-          <t>Feature-Level Fusion for RGB-T Detection</t>
+          <t>Cross-Attention Fusion for RGB-T Object Detection</t>
         </is>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>feature-level fusion for rgb-t detection</t>
+          <t>cross-attention fusion for rgb-t object detection</t>
         </is>
       </c>
       <c r="G116" t="inlineStr"/>
@@ -5011,12 +5011,12 @@
       </c>
       <c r="E117" t="inlineStr">
         <is>
-          <t>Decision-Level Fusion for RGB-T Systems</t>
+          <t>RGB-T Tracking via Graph Neural Networks</t>
         </is>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>decision-level fusion for rgb-t systems</t>
+          <t>rgb-t tracking via graph neural networks</t>
         </is>
       </c>
       <c r="G117" t="inlineStr"/>
@@ -5047,12 +5047,12 @@
       </c>
       <c r="E118" t="inlineStr">
         <is>
-          <t>Multimodal Learning for Object Detection</t>
+          <t>Multispectral Fusion for Low-Light Object Detection</t>
         </is>
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>multimodal learning for object detection</t>
+          <t>multispectral fusion for low-light object detection</t>
         </is>
       </c>
       <c r="G118" t="inlineStr"/>
@@ -5083,12 +5083,12 @@
       </c>
       <c r="E119" t="inlineStr">
         <is>
-          <t>RGB-T Tracking with Siamese Networks</t>
+          <t>Vision Transformer for RGB-T Semantic Segmentation</t>
         </is>
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>rgb-t tracking with siamese networks</t>
+          <t>vision transformer for rgb-t semantic segmentation</t>
         </is>
       </c>
       <c r="G119" t="inlineStr"/>
@@ -5119,12 +5119,12 @@
       </c>
       <c r="E120" t="inlineStr">
         <is>
-          <t>Sensor Fusion for Night-Time Detection</t>
+          <t>Feature-Level Fusion for Infrared-Visible Object Detection</t>
         </is>
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>sensor fusion for night-time detection</t>
+          <t>feature-level fusion for infrared-visible object detection</t>
         </is>
       </c>
       <c r="G120" t="inlineStr"/>
@@ -5155,12 +5155,12 @@
       </c>
       <c r="E121" t="inlineStr">
         <is>
-          <t>Cross-Modality Attention for RGB-T Fusion</t>
+          <t>Deep Fusion Model for RGB-T Tracking in Adverse Weather</t>
         </is>
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>cross-modality attention for rgb-t fusion</t>
+          <t>deep fusion model for rgb-t tracking in adverse weather</t>
         </is>
       </c>
       <c r="G121" t="inlineStr"/>
@@ -5191,12 +5191,12 @@
       </c>
       <c r="E122" t="inlineStr">
         <is>
-          <t>RGB-T Object Detection in Foggy Conditions</t>
+          <t>Multimodal Fusion for Nighttime Pedestrian Detection</t>
         </is>
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>rgb-t object detection in foggy conditions</t>
+          <t>multimodal fusion for nighttime pedestrian detection</t>
         </is>
       </c>
       <c r="G122" t="inlineStr"/>
@@ -5227,12 +5227,12 @@
       </c>
       <c r="E123" t="inlineStr">
         <is>
-          <t>Multimodal Segmentation for Urban Scenes</t>
+          <t>RGB-T Fusion with Self-Supervised Learning</t>
         </is>
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t>multimodal segmentation for urban scenes</t>
+          <t>rgb-t fusion with self-supervised learning</t>
         </is>
       </c>
       <c r="G123" t="inlineStr"/>
@@ -5263,12 +5263,12 @@
       </c>
       <c r="E124" t="inlineStr">
         <is>
-          <t>Deep Fusion Networks for RGB-T Perception</t>
+          <t>Attention Fusion Network for Thermal-Visible Detection</t>
         </is>
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t>deep fusion networks for rgb-t perception</t>
+          <t>attention fusion network for thermal-visible detection</t>
         </is>
       </c>
       <c r="G124" t="inlineStr"/>
@@ -5299,12 +5299,12 @@
       </c>
       <c r="E125" t="inlineStr">
         <is>
-          <t>Visible and Infrared Image Fusion Using Deep Learning</t>
+          <t>Cross-Domain RGB-T Fusion for Urban Scene Understanding</t>
         </is>
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t>visible and infrared image fusion using deep learning</t>
+          <t>cross-domain rgb-t fusion for urban scene understanding</t>
         </is>
       </c>
       <c r="G125" t="inlineStr"/>
@@ -5316,6 +5316,726 @@
       <c r="M125" t="inlineStr"/>
       <c r="N125" t="inlineStr"/>
     </row>
+    <row r="126">
+      <c r="A126" t="inlineStr">
+        <is>
+          <t>R0125</t>
+        </is>
+      </c>
+      <c r="B126" t="inlineStr"/>
+      <c r="C126" t="inlineStr">
+        <is>
+          <t>Google Scholar</t>
+        </is>
+      </c>
+      <c r="D126" t="inlineStr">
+        <is>
+          <t>Google Scholar</t>
+        </is>
+      </c>
+      <c r="E126" t="inlineStr">
+        <is>
+          <t>Low-Light Object Detection Using RGB-T Fusion Networks</t>
+        </is>
+      </c>
+      <c r="F126" t="inlineStr">
+        <is>
+          <t>low-light object detection using rgb-t fusion networks</t>
+        </is>
+      </c>
+      <c r="G126" t="inlineStr"/>
+      <c r="H126" t="inlineStr"/>
+      <c r="I126" t="inlineStr"/>
+      <c r="J126" t="inlineStr"/>
+      <c r="K126" t="inlineStr"/>
+      <c r="L126" t="inlineStr"/>
+      <c r="M126" t="inlineStr"/>
+      <c r="N126" t="inlineStr"/>
+    </row>
+    <row r="127">
+      <c r="A127" t="inlineStr">
+        <is>
+          <t>R0126</t>
+        </is>
+      </c>
+      <c r="B127" t="inlineStr"/>
+      <c r="C127" t="inlineStr">
+        <is>
+          <t>Google Scholar</t>
+        </is>
+      </c>
+      <c r="D127" t="inlineStr">
+        <is>
+          <t>Google Scholar</t>
+        </is>
+      </c>
+      <c r="E127" t="inlineStr">
+        <is>
+          <t>RGB-T Fusion with Adversarial Training for Robust Detection</t>
+        </is>
+      </c>
+      <c r="F127" t="inlineStr">
+        <is>
+          <t>rgb-t fusion with adversarial training for robust detection</t>
+        </is>
+      </c>
+      <c r="G127" t="inlineStr"/>
+      <c r="H127" t="inlineStr"/>
+      <c r="I127" t="inlineStr"/>
+      <c r="J127" t="inlineStr"/>
+      <c r="K127" t="inlineStr"/>
+      <c r="L127" t="inlineStr"/>
+      <c r="M127" t="inlineStr"/>
+      <c r="N127" t="inlineStr"/>
+    </row>
+    <row r="128">
+      <c r="A128" t="inlineStr">
+        <is>
+          <t>R0127</t>
+        </is>
+      </c>
+      <c r="B128" t="inlineStr"/>
+      <c r="C128" t="inlineStr">
+        <is>
+          <t>Google Scholar</t>
+        </is>
+      </c>
+      <c r="D128" t="inlineStr">
+        <is>
+          <t>Google Scholar</t>
+        </is>
+      </c>
+      <c r="E128" t="inlineStr">
+        <is>
+          <t>Multi-Level Fusion for Infrared and Visible Image Segmentation</t>
+        </is>
+      </c>
+      <c r="F128" t="inlineStr">
+        <is>
+          <t>multi-level fusion for infrared and visible image segmentation</t>
+        </is>
+      </c>
+      <c r="G128" t="inlineStr"/>
+      <c r="H128" t="inlineStr"/>
+      <c r="I128" t="inlineStr"/>
+      <c r="J128" t="inlineStr"/>
+      <c r="K128" t="inlineStr"/>
+      <c r="L128" t="inlineStr"/>
+      <c r="M128" t="inlineStr"/>
+      <c r="N128" t="inlineStr"/>
+    </row>
+    <row r="129">
+      <c r="A129" t="inlineStr">
+        <is>
+          <t>R0128</t>
+        </is>
+      </c>
+      <c r="B129" t="inlineStr"/>
+      <c r="C129" t="inlineStr">
+        <is>
+          <t>Google Scholar</t>
+        </is>
+      </c>
+      <c r="D129" t="inlineStr">
+        <is>
+          <t>Google Scholar</t>
+        </is>
+      </c>
+      <c r="E129" t="inlineStr">
+        <is>
+          <t>Deep Learning-Based RGB-T Fusion for Tracking Applications</t>
+        </is>
+      </c>
+      <c r="F129" t="inlineStr">
+        <is>
+          <t>deep learning-based rgb-t fusion for tracking applications</t>
+        </is>
+      </c>
+      <c r="G129" t="inlineStr"/>
+      <c r="H129" t="inlineStr"/>
+      <c r="I129" t="inlineStr"/>
+      <c r="J129" t="inlineStr"/>
+      <c r="K129" t="inlineStr"/>
+      <c r="L129" t="inlineStr"/>
+      <c r="M129" t="inlineStr"/>
+      <c r="N129" t="inlineStr"/>
+    </row>
+    <row r="130">
+      <c r="A130" t="inlineStr">
+        <is>
+          <t>R0129</t>
+        </is>
+      </c>
+      <c r="B130" t="inlineStr"/>
+      <c r="C130" t="inlineStr">
+        <is>
+          <t>Google Scholar</t>
+        </is>
+      </c>
+      <c r="D130" t="inlineStr">
+        <is>
+          <t>Google Scholar</t>
+        </is>
+      </c>
+      <c r="E130" t="inlineStr">
+        <is>
+          <t>Semantic Segmentation of Night Scenes Using RGB-T Data</t>
+        </is>
+      </c>
+      <c r="F130" t="inlineStr">
+        <is>
+          <t>semantic segmentation of night scenes using rgb-t data</t>
+        </is>
+      </c>
+      <c r="G130" t="inlineStr"/>
+      <c r="H130" t="inlineStr"/>
+      <c r="I130" t="inlineStr"/>
+      <c r="J130" t="inlineStr"/>
+      <c r="K130" t="inlineStr"/>
+      <c r="L130" t="inlineStr"/>
+      <c r="M130" t="inlineStr"/>
+      <c r="N130" t="inlineStr"/>
+    </row>
+    <row r="131">
+      <c r="A131" t="inlineStr">
+        <is>
+          <t>R0130</t>
+        </is>
+      </c>
+      <c r="B131" t="inlineStr"/>
+      <c r="C131" t="inlineStr">
+        <is>
+          <t>Google Scholar</t>
+        </is>
+      </c>
+      <c r="D131" t="inlineStr">
+        <is>
+          <t>Google Scholar</t>
+        </is>
+      </c>
+      <c r="E131" t="inlineStr">
+        <is>
+          <t>Fusion-Based Perception for Autonomous Vehicles in Fog</t>
+        </is>
+      </c>
+      <c r="F131" t="inlineStr">
+        <is>
+          <t>fusion-based perception for autonomous vehicles in fog</t>
+        </is>
+      </c>
+      <c r="G131" t="inlineStr"/>
+      <c r="H131" t="inlineStr"/>
+      <c r="I131" t="inlineStr"/>
+      <c r="J131" t="inlineStr"/>
+      <c r="K131" t="inlineStr"/>
+      <c r="L131" t="inlineStr"/>
+      <c r="M131" t="inlineStr"/>
+      <c r="N131" t="inlineStr"/>
+    </row>
+    <row r="132">
+      <c r="A132" t="inlineStr">
+        <is>
+          <t>R0131</t>
+        </is>
+      </c>
+      <c r="B132" t="inlineStr"/>
+      <c r="C132" t="inlineStr">
+        <is>
+          <t>Google Scholar</t>
+        </is>
+      </c>
+      <c r="D132" t="inlineStr">
+        <is>
+          <t>Google Scholar</t>
+        </is>
+      </c>
+      <c r="E132" t="inlineStr">
+        <is>
+          <t>RGB-T Fusion for Object Detection Using CNN-Transformer Hybrid</t>
+        </is>
+      </c>
+      <c r="F132" t="inlineStr">
+        <is>
+          <t>rgb-t fusion for object detection using cnn-transformer hybrid</t>
+        </is>
+      </c>
+      <c r="G132" t="inlineStr"/>
+      <c r="H132" t="inlineStr"/>
+      <c r="I132" t="inlineStr"/>
+      <c r="J132" t="inlineStr"/>
+      <c r="K132" t="inlineStr"/>
+      <c r="L132" t="inlineStr"/>
+      <c r="M132" t="inlineStr"/>
+      <c r="N132" t="inlineStr"/>
+    </row>
+    <row r="133">
+      <c r="A133" t="inlineStr">
+        <is>
+          <t>R0132</t>
+        </is>
+      </c>
+      <c r="B133" t="inlineStr"/>
+      <c r="C133" t="inlineStr">
+        <is>
+          <t>Google Scholar</t>
+        </is>
+      </c>
+      <c r="D133" t="inlineStr">
+        <is>
+          <t>Google Scholar</t>
+        </is>
+      </c>
+      <c r="E133" t="inlineStr">
+        <is>
+          <t>Cross-Modality Learning for RGB-T Detection</t>
+        </is>
+      </c>
+      <c r="F133" t="inlineStr">
+        <is>
+          <t>cross-modality learning for rgb-t detection</t>
+        </is>
+      </c>
+      <c r="G133" t="inlineStr"/>
+      <c r="H133" t="inlineStr"/>
+      <c r="I133" t="inlineStr"/>
+      <c r="J133" t="inlineStr"/>
+      <c r="K133" t="inlineStr"/>
+      <c r="L133" t="inlineStr"/>
+      <c r="M133" t="inlineStr"/>
+      <c r="N133" t="inlineStr"/>
+    </row>
+    <row r="134">
+      <c r="A134" t="inlineStr">
+        <is>
+          <t>R0133</t>
+        </is>
+      </c>
+      <c r="B134" t="inlineStr"/>
+      <c r="C134" t="inlineStr">
+        <is>
+          <t>Google Scholar</t>
+        </is>
+      </c>
+      <c r="D134" t="inlineStr">
+        <is>
+          <t>Google Scholar</t>
+        </is>
+      </c>
+      <c r="E134" t="inlineStr">
+        <is>
+          <t>Multimodal RGB-T Tracking with Attention Mechanisms</t>
+        </is>
+      </c>
+      <c r="F134" t="inlineStr">
+        <is>
+          <t>multimodal rgb-t tracking with attention mechanisms</t>
+        </is>
+      </c>
+      <c r="G134" t="inlineStr"/>
+      <c r="H134" t="inlineStr"/>
+      <c r="I134" t="inlineStr"/>
+      <c r="J134" t="inlineStr"/>
+      <c r="K134" t="inlineStr"/>
+      <c r="L134" t="inlineStr"/>
+      <c r="M134" t="inlineStr"/>
+      <c r="N134" t="inlineStr"/>
+    </row>
+    <row r="135">
+      <c r="A135" t="inlineStr">
+        <is>
+          <t>R0134</t>
+        </is>
+      </c>
+      <c r="B135" t="inlineStr"/>
+      <c r="C135" t="inlineStr">
+        <is>
+          <t>Google Scholar</t>
+        </is>
+      </c>
+      <c r="D135" t="inlineStr">
+        <is>
+          <t>Google Scholar</t>
+        </is>
+      </c>
+      <c r="E135" t="inlineStr">
+        <is>
+          <t>Robust Multispectral Detection for Low-Visibility Environments</t>
+        </is>
+      </c>
+      <c r="F135" t="inlineStr">
+        <is>
+          <t>robust multispectral detection for low-visibility environments</t>
+        </is>
+      </c>
+      <c r="G135" t="inlineStr"/>
+      <c r="H135" t="inlineStr"/>
+      <c r="I135" t="inlineStr"/>
+      <c r="J135" t="inlineStr"/>
+      <c r="K135" t="inlineStr"/>
+      <c r="L135" t="inlineStr"/>
+      <c r="M135" t="inlineStr"/>
+      <c r="N135" t="inlineStr"/>
+    </row>
+    <row r="136">
+      <c r="A136" t="inlineStr">
+        <is>
+          <t>R0135</t>
+        </is>
+      </c>
+      <c r="B136" t="inlineStr"/>
+      <c r="C136" t="inlineStr">
+        <is>
+          <t>Google Scholar</t>
+        </is>
+      </c>
+      <c r="D136" t="inlineStr">
+        <is>
+          <t>Google Scholar</t>
+        </is>
+      </c>
+      <c r="E136" t="inlineStr">
+        <is>
+          <t>RGB-T Fusion for Real-Time Object Detection</t>
+        </is>
+      </c>
+      <c r="F136" t="inlineStr">
+        <is>
+          <t>rgb-t fusion for real-time object detection</t>
+        </is>
+      </c>
+      <c r="G136" t="inlineStr"/>
+      <c r="H136" t="inlineStr"/>
+      <c r="I136" t="inlineStr"/>
+      <c r="J136" t="inlineStr"/>
+      <c r="K136" t="inlineStr"/>
+      <c r="L136" t="inlineStr"/>
+      <c r="M136" t="inlineStr"/>
+      <c r="N136" t="inlineStr"/>
+    </row>
+    <row r="137">
+      <c r="A137" t="inlineStr">
+        <is>
+          <t>R0136</t>
+        </is>
+      </c>
+      <c r="B137" t="inlineStr"/>
+      <c r="C137" t="inlineStr">
+        <is>
+          <t>Google Scholar</t>
+        </is>
+      </c>
+      <c r="D137" t="inlineStr">
+        <is>
+          <t>Google Scholar</t>
+        </is>
+      </c>
+      <c r="E137" t="inlineStr">
+        <is>
+          <t>Deep Multimodal Perception for Autonomous Driving in Night Conditions</t>
+        </is>
+      </c>
+      <c r="F137" t="inlineStr">
+        <is>
+          <t>deep multimodal perception for autonomous driving in night conditions</t>
+        </is>
+      </c>
+      <c r="G137" t="inlineStr"/>
+      <c r="H137" t="inlineStr"/>
+      <c r="I137" t="inlineStr"/>
+      <c r="J137" t="inlineStr"/>
+      <c r="K137" t="inlineStr"/>
+      <c r="L137" t="inlineStr"/>
+      <c r="M137" t="inlineStr"/>
+      <c r="N137" t="inlineStr"/>
+    </row>
+    <row r="138">
+      <c r="A138" t="inlineStr">
+        <is>
+          <t>R0137</t>
+        </is>
+      </c>
+      <c r="B138" t="inlineStr"/>
+      <c r="C138" t="inlineStr">
+        <is>
+          <t>Google Scholar</t>
+        </is>
+      </c>
+      <c r="D138" t="inlineStr">
+        <is>
+          <t>Google Scholar</t>
+        </is>
+      </c>
+      <c r="E138" t="inlineStr">
+        <is>
+          <t>Fusion-Based Segmentation for Thermal-Visible Images</t>
+        </is>
+      </c>
+      <c r="F138" t="inlineStr">
+        <is>
+          <t>fusion-based segmentation for thermal-visible images</t>
+        </is>
+      </c>
+      <c r="G138" t="inlineStr"/>
+      <c r="H138" t="inlineStr"/>
+      <c r="I138" t="inlineStr"/>
+      <c r="J138" t="inlineStr"/>
+      <c r="K138" t="inlineStr"/>
+      <c r="L138" t="inlineStr"/>
+      <c r="M138" t="inlineStr"/>
+      <c r="N138" t="inlineStr"/>
+    </row>
+    <row r="139">
+      <c r="A139" t="inlineStr">
+        <is>
+          <t>R0138</t>
+        </is>
+      </c>
+      <c r="B139" t="inlineStr"/>
+      <c r="C139" t="inlineStr">
+        <is>
+          <t>Google Scholar</t>
+        </is>
+      </c>
+      <c r="D139" t="inlineStr">
+        <is>
+          <t>Google Scholar</t>
+        </is>
+      </c>
+      <c r="E139" t="inlineStr">
+        <is>
+          <t>RGB-T Fusion Using Self-Attention Mechanisms</t>
+        </is>
+      </c>
+      <c r="F139" t="inlineStr">
+        <is>
+          <t>rgb-t fusion using self-attention mechanisms</t>
+        </is>
+      </c>
+      <c r="G139" t="inlineStr"/>
+      <c r="H139" t="inlineStr"/>
+      <c r="I139" t="inlineStr"/>
+      <c r="J139" t="inlineStr"/>
+      <c r="K139" t="inlineStr"/>
+      <c r="L139" t="inlineStr"/>
+      <c r="M139" t="inlineStr"/>
+      <c r="N139" t="inlineStr"/>
+    </row>
+    <row r="140">
+      <c r="A140" t="inlineStr">
+        <is>
+          <t>R0139</t>
+        </is>
+      </c>
+      <c r="B140" t="inlineStr"/>
+      <c r="C140" t="inlineStr">
+        <is>
+          <t>Google Scholar</t>
+        </is>
+      </c>
+      <c r="D140" t="inlineStr">
+        <is>
+          <t>Google Scholar</t>
+        </is>
+      </c>
+      <c r="E140" t="inlineStr">
+        <is>
+          <t>Multimodal Tracking in Low-Light Conditions Using RGB-T Data</t>
+        </is>
+      </c>
+      <c r="F140" t="inlineStr">
+        <is>
+          <t>multimodal tracking in low-light conditions using rgb-t data</t>
+        </is>
+      </c>
+      <c r="G140" t="inlineStr"/>
+      <c r="H140" t="inlineStr"/>
+      <c r="I140" t="inlineStr"/>
+      <c r="J140" t="inlineStr"/>
+      <c r="K140" t="inlineStr"/>
+      <c r="L140" t="inlineStr"/>
+      <c r="M140" t="inlineStr"/>
+      <c r="N140" t="inlineStr"/>
+    </row>
+    <row r="141">
+      <c r="A141" t="inlineStr">
+        <is>
+          <t>R0140</t>
+        </is>
+      </c>
+      <c r="B141" t="inlineStr"/>
+      <c r="C141" t="inlineStr">
+        <is>
+          <t>Google Scholar</t>
+        </is>
+      </c>
+      <c r="D141" t="inlineStr">
+        <is>
+          <t>Google Scholar</t>
+        </is>
+      </c>
+      <c r="E141" t="inlineStr">
+        <is>
+          <t>Infrared-Visible Fusion for Pedestrian Detection in Fog</t>
+        </is>
+      </c>
+      <c r="F141" t="inlineStr">
+        <is>
+          <t>infrared-visible fusion for pedestrian detection in fog</t>
+        </is>
+      </c>
+      <c r="G141" t="inlineStr"/>
+      <c r="H141" t="inlineStr"/>
+      <c r="I141" t="inlineStr"/>
+      <c r="J141" t="inlineStr"/>
+      <c r="K141" t="inlineStr"/>
+      <c r="L141" t="inlineStr"/>
+      <c r="M141" t="inlineStr"/>
+      <c r="N141" t="inlineStr"/>
+    </row>
+    <row r="142">
+      <c r="A142" t="inlineStr">
+        <is>
+          <t>R0141</t>
+        </is>
+      </c>
+      <c r="B142" t="inlineStr"/>
+      <c r="C142" t="inlineStr">
+        <is>
+          <t>Google Scholar</t>
+        </is>
+      </c>
+      <c r="D142" t="inlineStr">
+        <is>
+          <t>Google Scholar</t>
+        </is>
+      </c>
+      <c r="E142" t="inlineStr">
+        <is>
+          <t>RGB-T Fusion for Scene Understanding in Smart Cities</t>
+        </is>
+      </c>
+      <c r="F142" t="inlineStr">
+        <is>
+          <t>rgb-t fusion for scene understanding in smart cities</t>
+        </is>
+      </c>
+      <c r="G142" t="inlineStr"/>
+      <c r="H142" t="inlineStr"/>
+      <c r="I142" t="inlineStr"/>
+      <c r="J142" t="inlineStr"/>
+      <c r="K142" t="inlineStr"/>
+      <c r="L142" t="inlineStr"/>
+      <c r="M142" t="inlineStr"/>
+      <c r="N142" t="inlineStr"/>
+    </row>
+    <row r="143">
+      <c r="A143" t="inlineStr">
+        <is>
+          <t>R0142</t>
+        </is>
+      </c>
+      <c r="B143" t="inlineStr"/>
+      <c r="C143" t="inlineStr">
+        <is>
+          <t>Google Scholar</t>
+        </is>
+      </c>
+      <c r="D143" t="inlineStr">
+        <is>
+          <t>Google Scholar</t>
+        </is>
+      </c>
+      <c r="E143" t="inlineStr">
+        <is>
+          <t>Cross-Modal Fusion for Thermal and Visible Object Detection</t>
+        </is>
+      </c>
+      <c r="F143" t="inlineStr">
+        <is>
+          <t>cross-modal fusion for thermal and visible object detection</t>
+        </is>
+      </c>
+      <c r="G143" t="inlineStr"/>
+      <c r="H143" t="inlineStr"/>
+      <c r="I143" t="inlineStr"/>
+      <c r="J143" t="inlineStr"/>
+      <c r="K143" t="inlineStr"/>
+      <c r="L143" t="inlineStr"/>
+      <c r="M143" t="inlineStr"/>
+      <c r="N143" t="inlineStr"/>
+    </row>
+    <row r="144">
+      <c r="A144" t="inlineStr">
+        <is>
+          <t>R0143</t>
+        </is>
+      </c>
+      <c r="B144" t="inlineStr"/>
+      <c r="C144" t="inlineStr">
+        <is>
+          <t>Google Scholar</t>
+        </is>
+      </c>
+      <c r="D144" t="inlineStr">
+        <is>
+          <t>Google Scholar</t>
+        </is>
+      </c>
+      <c r="E144" t="inlineStr">
+        <is>
+          <t>Transformer-Based Multimodal Fusion for RGB-T Segmentation</t>
+        </is>
+      </c>
+      <c r="F144" t="inlineStr">
+        <is>
+          <t>transformer-based multimodal fusion for rgb-t segmentation</t>
+        </is>
+      </c>
+      <c r="G144" t="inlineStr"/>
+      <c r="H144" t="inlineStr"/>
+      <c r="I144" t="inlineStr"/>
+      <c r="J144" t="inlineStr"/>
+      <c r="K144" t="inlineStr"/>
+      <c r="L144" t="inlineStr"/>
+      <c r="M144" t="inlineStr"/>
+      <c r="N144" t="inlineStr"/>
+    </row>
+    <row r="145">
+      <c r="A145" t="inlineStr">
+        <is>
+          <t>R0144</t>
+        </is>
+      </c>
+      <c r="B145" t="inlineStr"/>
+      <c r="C145" t="inlineStr">
+        <is>
+          <t>Google Scholar</t>
+        </is>
+      </c>
+      <c r="D145" t="inlineStr">
+        <is>
+          <t>Google Scholar</t>
+        </is>
+      </c>
+      <c r="E145" t="inlineStr">
+        <is>
+          <t>State-of-the-Art RGB-T Fusion Techniques for Adverse Weather Detection</t>
+        </is>
+      </c>
+      <c r="F145" t="inlineStr">
+        <is>
+          <t>state-of-the-art rgb-t fusion techniques for adverse weather detection</t>
+        </is>
+      </c>
+      <c r="G145" t="inlineStr"/>
+      <c r="H145" t="inlineStr"/>
+      <c r="I145" t="inlineStr"/>
+      <c r="J145" t="inlineStr"/>
+      <c r="K145" t="inlineStr"/>
+      <c r="L145" t="inlineStr"/>
+      <c r="M145" t="inlineStr"/>
+      <c r="N145" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
